--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37019DCE-E550-4C44-957C-A345C684F486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818F07B7-A026-4879-B816-0A19701A3835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15210" yWindow="1080" windowWidth="13335" windowHeight="14430" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="14280" yWindow="30" windowWidth="14445" windowHeight="15105" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="171">
   <si>
     <t>major</t>
   </si>
@@ -55,264 +55,6 @@
     <t>VERSION_INFO</t>
   </si>
   <si>
-    <t>"Modificado o campo Dias para permitir 1/2 diária",</t>
-  </si>
-  <si>
-    <t>"Adicionado campo com ID do lançamento",</t>
-  </si>
-  <si>
-    <t>"Refeita a verificação se a planilha está aberta"</t>
-  </si>
-  <si>
-    <t>"Separação de despesas com funcionários, no Relatório, separando despesas mensais das eventuais"</t>
-  </si>
-  <si>
-    <t>"Correção do campo percentual e inclusão de dados bancários na Entrada em Gestão de Contrato"</t>
-  </si>
-  <si>
-    <t>Melhoria do layout da tela de Seleção de Cliente"</t>
-  </si>
-  <si>
-    <t>Correção da combobox Banco em Fornecedor"</t>
-  </si>
-  <si>
-    <t>"Reorganização da aba Fornecedor com funcionalidade de duplo clique"</t>
-  </si>
-  <si>
-    <t>"Ajuste do layout da aba Entrada de Dados para melhor usabilidade"</t>
-  </si>
-  <si>
-    <t>"Adição de preenchimento automático da referência baseado na especificação do fornecedor"</t>
-  </si>
-  <si>
-    <t>"Criação do módulo para rateio de despesas comuns a todos os clientes"</t>
-  </si>
-  <si>
-    <t>"Criação do módulo de controle de medições de empreiteiros"</t>
-  </si>
-  <si>
-    <t>"Ajuste na aba Clientes, permitindo a inclusão do témino da obra ou do contrato"</t>
-  </si>
-  <si>
-    <t>"Criação de uma interface com todos os relatórios"</t>
-  </si>
-  <si>
-    <t>"Criação de relatório de Fornecedores",</t>
-  </si>
-  <si>
-    <t>"Criação de relatório de Medições",</t>
-  </si>
-  <si>
-    <t>"Criação de relatório de Tipos de Despesas"</t>
-  </si>
-  <si>
-    <t>"Separação de relatório de Lançamentos Futuros"</t>
-  </si>
-  <si>
-    <t>"Inclusão das etapas de obra nos contratos de administração de obras"</t>
-  </si>
-  <si>
-    <r>
-      <t>"Incluído Gerenciador de lançamentos, permitindo edição e exclusão de dados da planilha"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF292929"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <t>"Liberado Relatório por Categoria"</t>
-  </si>
-  <si>
-    <t>"Adicionados campos na planilha com 'STATUS', 'ID_LANCAMENTO' e 'HISTORICO_ALTERACAO'",</t>
-  </si>
-  <si>
-    <t>"Modificados todos relatórios para identificar o 'STATUS' dos lançamentos",</t>
-  </si>
-  <si>
-    <t>"Instalado sistema de Backup Automático contra quedas/travamentos"</t>
-  </si>
-  <si>
-    <t>"Melhoria no relatório de Tipos de Despesas, mostrando o total geral por tipo e gráfico de linha do tempo"</t>
-  </si>
-  <si>
-    <t>"Melhoria no relatório de Categoria, mostrando o total geral por categoria e gráfico de linha do tempo"</t>
-  </si>
-  <si>
-    <t>"Inclusão de Visualizador de Lançamentos de Fornecedor"</t>
-  </si>
-  <si>
-    <t>"Inclusão de Correção Monetária para contratos de administração, dependendo de teste para ser totalmente implementada."</t>
-  </si>
-  <si>
-    <t>"Adicão de funcionalidade para cadastro de fornecedor PF sem CPF"</t>
-  </si>
-  <si>
-    <t>"Melhoria no Relatório de Fornecedores com a inclusão de opção para mostrar quais clientes adquiriram itens de um dado fornecedor "</t>
-  </si>
-  <si>
-    <t>"Alteração do Relatório de Despesas para incluir o PDF Temporário"</t>
-  </si>
-  <si>
-    <t>"Exclusão do ordenamento dos pagamentos de Diaristas para ser pela entrada e não por valor pago"</t>
-  </si>
-  <si>
-    <t>"Exclusão do ordenamento dos pagamentos das despesas pagas pelo Cliente para ser pela entrada e não por data de vencimento"</t>
-  </si>
-  <si>
-    <t>"Inclusão de Importação de planilha com dados de TRANSPORTE e CAFÉ"</t>
-  </si>
-  <si>
-    <t>"Adição de funcionalidade para recálculo de taxa de administração por percentual, sempre que houver inclusão, alteração ou exclusão de lançamento"</t>
-  </si>
-  <si>
-    <t>"Melhoria na funcionalidade que detecta duplicidade de lançamento"</t>
-  </si>
-  <si>
-    <t>"Correção do cálculo de taxa de administração, considerando apenas lançamentos do tipo 'ATIVO'."</t>
-  </si>
-  <si>
-    <t>"Inclusão do campo 'NF' no Gerenciador de Lançamentos"</t>
-  </si>
-  <si>
-    <t>"Inclusão de botões de 'EXCLUSÃO/RESTAURAÇÃO' de várias despesas no Gerenciador de Lançamentos."</t>
-  </si>
-  <si>
-    <t>"Inclusão do campo 'ETAPA DA OBRA' na Entrada de Dados, com manutenção através das Configurações do Sistema."</t>
-  </si>
-  <si>
-    <r>
-      <t>"Inclusão de gerenciamento para excluir CPF temporário"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF292929"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <t>"Inclusão de campo 'INSUMO' na Entrada de Dados, com manutenção através das Configurações do Sistema",</t>
-  </si>
-  <si>
-    <t>"Melhoria no Visualizador de Lançamentos de Fornecedor que agora possui todas as funcionalidades do Gerenciador de Lançamentos"</t>
-  </si>
-  <si>
-    <t>"Correção na aba Entrada de Dados que não estava limpando corretamente todos os campos"</t>
-  </si>
-  <si>
-    <t>"Correção do Backup Automático para verificar o Cliente antes de salvar"</t>
-  </si>
-  <si>
-    <t>"Inclusão de autocompletar nos campos 'Etapa da Obra' e 'Insumo' na aba Entrada de Dados"</t>
-  </si>
-  <si>
-    <t>"Correção de EXCLUIR/RESTAURAR individual no Gerenciador de Lançamentos"</t>
-  </si>
-  <si>
-    <t>"Inclusão da opção Dinheiro em Dados Bancários na entrada de dados"</t>
-  </si>
-  <si>
-    <t>Melhorias no parcelamento, permitindo a entrada de parcelas com diferentes valores"</t>
-  </si>
-  <si>
-    <t>"Inclusão de Agenda com dados pré-definidos e lançamentos futuros"</t>
-  </si>
-  <si>
-    <t>"Correção do filtro de datas do Gerenciador de Lançamentos, que estava trazendo a data do dia se, outras funcionalidades fossem chamadas."</t>
-  </si>
-  <si>
-    <t>"Inclusão de edição de Taxa de Administração do tipo Fixo"</t>
-  </si>
-  <si>
-    <t>"Melhoria no Visualizador de Lançamentos de Pendentes, que elimina registros duplicados ao salvar na planilha"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Correção da compensação de Taxa de Administração caso fossem detectados valores errados em períodos anteriores" </t>
-  </si>
-  <si>
-    <t>"Correção na importação de dados de RH após mudança de versão do Excel na origem do arquivo"</t>
-  </si>
-  <si>
-    <t>"Disponibilizada a importação da planilha de RH oriúnda do sistema Domínio"</t>
-  </si>
-  <si>
-    <r>
-      <t>"Inclusão de campo para Notas no final do relatório"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF292929"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <t>"Correção para inclusão de lançamentos futuros no relatório"</t>
-  </si>
-  <si>
-    <t>"Inclusão de vinculação de medições de contratos à despesa lançada",</t>
-  </si>
-  <si>
-    <t>"Adição de diferenciação visual entre ambientes TESTE e PRODUÇÃO"</t>
-  </si>
-  <si>
-    <t>"Inclusão de funcionalidade para importação de NFe via XML e Chave de Acesso, permitindo salvar dados financeiros e materiais na planilha do cliente"</t>
-  </si>
-  <si>
-    <r>
-      <t>"Inclusão de Etapa da Obra nas importações de dados de RH - Folha e Transporte &amp; Café"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF292929"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <t>"Inclusão da opção de remover vários regitros de uma vez só no Visualizador de Lançamentos",</t>
-  </si>
-  <si>
-    <t>"Inclusão da opção de vincular parcelas do contrato de administração de obra a lançamentos efetuados",</t>
-  </si>
-  <si>
-    <t>"Relatório de Despesas Aprimorado: adição de numeração de páginas",</t>
-  </si>
-  <si>
-    <t>"Relatório de Despesas Aprimorado: mudança de Notas para a primeira página e arquivada na planilha do cliente",</t>
-  </si>
-  <si>
-    <t>"Relatório de Despesas Aprimorado: adição de data de vencimento para 13º, Férias e Rescisão",</t>
-  </si>
-  <si>
-    <t>"Mudança do botão 'Visualizar Lançamentos' para a seção de Gerenciamento de Dados"</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>"Correção dos dados bancários na Agenda",</t>
-    </r>
-  </si>
-  <si>
     <t>Incluída a opção de editar em massa no visualizador.</t>
   </si>
   <si>
@@ -335,9 +77,6 @@
   </si>
   <si>
     <t>Incluído Data Fim nos contratos de empreiteiros</t>
-  </si>
-  <si>
-    <t>Alteração do texto "Complemento de Caixa" para "Despesas pagas pelo Caixa" no Relatório de Despesas</t>
   </si>
   <si>
     <t>Incluída a opção de copiar as fases/eventos de um gestor para outro no contrato de administração de obra</t>
@@ -507,12 +246,351 @@
   <si>
     <t>Inclusão de Relatório Modelo para exportar para Excel quando não houver contrato de medição cadastrado</t>
   </si>
+  <si>
+    <t>Adição de funcionalidade para recálculo de taxa de administração por percentual, sempre que houver inclusão, alteração ou exclusão de lançamento</t>
+  </si>
+  <si>
+    <t>Melhoria na funcionalidade que detecta duplicidade de lançamento</t>
+  </si>
+  <si>
+    <t>Adição de funcionalidade para recálculo de taxa de administração por percentual, sempre que houver inclusão, alteração ou exclusão de lançamento,</t>
+  </si>
+  <si>
+    <t>Correção do cálculo de taxa de administração, considerando apenas lançamentos do tipo 'ATIVO',</t>
+  </si>
+  <si>
+    <t>Melhoria na funcionalidade que detecta duplicidade de lançamento,</t>
+  </si>
+  <si>
+    <t>Inclusão do campo 'NF' no Gerenciador de Lançamentos,</t>
+  </si>
+  <si>
+    <t>Inclusão de botões de 'EXCLUSÃO/RESTAURAÇÃO' de várias despesas no Gerenciador de Lançamentos,</t>
+  </si>
+  <si>
+    <t>Inclusão do campo 'ETAPA DA OBRA' na Entrada de Dados, com manutenção através das Configurações do Sistema,</t>
+  </si>
+  <si>
+    <t>Inclusão de gerenciamento para excluir CPF temporário,</t>
+  </si>
+  <si>
+    <t>Inclusão de campo 'INSUMO' na Entrada de Dados, com manutenção através das Configurações do Sistema,</t>
+  </si>
+  <si>
+    <t>Inclusão de funcionalidade para importaçãoo de NFe via XML e Chave de Acesso, permitindo salvar dados financeiros e materiais na planilha do cliente</t>
+  </si>
+  <si>
+    <t>Melhoria no Relatório de Medições, exportado do sistema, com índice, próximo ID e lista de fornecedores co Vínculo = EMPREITEIRO,</t>
+  </si>
+  <si>
+    <t>Correção no relatório que compara a gestão de Medições e Taxa de Administração com registros em Dados,</t>
+  </si>
+  <si>
+    <t>Inclusão de Relatório Modelo para exportar para Excel quando não houver contrato de medição cadastrado,</t>
+  </si>
+  <si>
+    <t>Inclusão de Importação de DIÁRIAS de Colaboradores,</t>
+  </si>
+  <si>
+    <t>Eliminação do arquivo MODELO.xlsx, agora o sistema gera a planilha do cliente, garantindo compatibilidade e melhorias contínuas,</t>
+  </si>
+  <si>
+    <t>Alterado o cálculo do número do Relatório de Despesas, considerando a data de lançamento mais antiga,</t>
+  </si>
+  <si>
+    <t>Incluído o Nº do Relatório na consulta por Fornecedor</t>
+  </si>
+  <si>
+    <t>Inclusão de Importação de DIÁRIAS de Colaboradores, com data de vencimento,</t>
+  </si>
+  <si>
+    <t>Incluído o Nº do Relatório na consulta por Fornecedor,</t>
+  </si>
+  <si>
+    <t>Correções pontuais no Contrato de Prestação de Serviços</t>
+  </si>
+  <si>
+    <t>Cadastro de cliente — checkboxes para marcar fictício/vinculado e caixa controlado, com as abas de controle nascendo junto (ou confirmação explícita, se for num cliente já existente),</t>
+  </si>
+  <si>
+    <t>Repasse Mão de Obra (clientes fictícios) — cálculo, painel na tela, botão de registro, bloco no PDF,</t>
+  </si>
+  <si>
+    <t>Saldo Caixa de Obra (clientes reais com conta controlada) — cálculo, painel na tela, botão de registro, bloco no PDF,</t>
+  </si>
+  <si>
+    <t>Layout — melhoria nas telas de criar/editar cliente compactadas, sem os espaços tortos</t>
+  </si>
+  <si>
+    <t>Cadastro de cliente — está gerando cadastro na base de fornecedores, sempre que marcado,</t>
+  </si>
+  <si>
+    <t>Gerenciador: Corrigida a falha de Edição em Massa,</t>
+  </si>
+  <si>
+    <t>Visualizador: liberada a edição de dados bancários,</t>
+  </si>
+  <si>
+    <t>Saldo Caixa de Obra: adaptado para aceitar valores negativos,</t>
+  </si>
+  <si>
+    <t>Contrato de Empreiteiros trazendo Razão Social e Nome, quando diferentes, e com multa inicial R$0,00,</t>
+  </si>
+  <si>
+    <t>Funcionalidade desenvolvida para permitir manter cliente quando mudar de Entrada de Dados para Gestão de Medições e vice-e-versa,</t>
+  </si>
+  <si>
+    <t>Agenda: Confirmação em massa rápidasempre que houver valor no registro,</t>
+  </si>
+  <si>
+    <t>Agenda: Edição de dados bancários, quando necessário, apenas para o registro confirmado,</t>
+  </si>
+  <si>
+    <t>Correção na importação de Diárias para aceitar 1/2 diária,</t>
+  </si>
+  <si>
+    <t>Relatório de Medições, no módulo Gestão de Medições, com data sugerida,</t>
+  </si>
+  <si>
+    <t>Relatório de Medições corrigido no módulo de Relatórios</t>
+  </si>
+  <si>
+    <t>Saldo Caixa de Obra: adaptado para pagar todas as despesas, se necessário,</t>
+  </si>
+  <si>
+    <t>Relatório de Medições sem mudança de página enre dados do contrato e seu extrato,</t>
+  </si>
+  <si>
+    <t>Gestão de Medições: correção do método de edição de medições,</t>
+  </si>
+  <si>
+    <t>Função nova: Regularização de dados fiscais, razaão social e nome, em base de fornecedores em todos os arquivos onde existam dados a serem corrigidos,</t>
+  </si>
+  <si>
+    <t>Função nova: Mesclar fornecedores duplicados, mantendo apenas um registro e atualizando todos os arquivos relacionados</t>
+  </si>
+  <si>
+    <t>Gerador de comprovante de pagamento de Transporte e Café,</t>
+  </si>
+  <si>
+    <t>Correção do Editor do Visualizar Lançamentos, que estava alterando a data do relatório,</t>
+  </si>
+  <si>
+    <t>Medições: a ferramenta Vincular traz todos os registros que atendam aos requisitos, mesmo valores menores do que a da medição que se quer vincular</t>
+  </si>
+  <si>
+    <t>Inclusão de validação de dados de colaboradores ao importar Transporte, Folha RH e Diárias, corrigindo ou incluindo na Base_fornecedores.xlsx,</t>
+  </si>
+  <si>
+    <t>Permite reemitir folha de rosto ou relatório inteiro, em sua totalidade ou por período do Relatório Quinzenal de Despesas,</t>
+  </si>
+  <si>
+    <t>Retirada de Lançamentos Futuros e remoção da saída em Excel do Relatório Quinzenal</t>
+  </si>
+  <si>
+    <t>Separação de despesas com funcionários, no Relatório, separando despesas mensais das eventuais</t>
+  </si>
+  <si>
+    <t>Correção do campo percentual e inclusão de dados bancários na Entrada em Gestão de Contrato</t>
+  </si>
+  <si>
+    <t>Melhoria do layout da tela de Seleção de Cliente</t>
+  </si>
+  <si>
+    <t>Correção da combobox Banco em Fornecedor</t>
+  </si>
+  <si>
+    <t>Reorganização da aba Fornecedor com funcionalidade de duplo clique</t>
+  </si>
+  <si>
+    <t>Ajuste do layout da aba Entrada de Dados para melhor usabilidade</t>
+  </si>
+  <si>
+    <t>Adição de preenchimento automático da referência baseado na especificação do fornecedor</t>
+  </si>
+  <si>
+    <t>Criação do módulo para rateio de despesas comuns a todos os clientes</t>
+  </si>
+  <si>
+    <t>Criação do módulo de controle de medições de empreiteiros</t>
+  </si>
+  <si>
+    <t>Ajuste na aba Clientes, permitindo a inclusão do témino da obra ou do contrato</t>
+  </si>
+  <si>
+    <t>Criação de uma interface com todos os relatórios</t>
+  </si>
+  <si>
+    <t>Criação de relatório de Fornecedores,</t>
+  </si>
+  <si>
+    <t>Criação de relatório de Medições,</t>
+  </si>
+  <si>
+    <t>Criação de relatório de Tipos de Despesas</t>
+  </si>
+  <si>
+    <t>Separação de relatório de Lançamentos Futuros</t>
+  </si>
+  <si>
+    <t>Inclusão das etapas de obra nos contratos de administração de obras</t>
+  </si>
+  <si>
+    <t>Disponibilizada a importação da planilha de RH oriúnda do sistema Domínio</t>
+  </si>
+  <si>
+    <t>Modificado o campo Dias para permitir 1/2 diária,</t>
+  </si>
+  <si>
+    <t>Adicionado campo com ID do lançamento,</t>
+  </si>
+  <si>
+    <t>Refeita a verificação se a planilha está aberta</t>
+  </si>
+  <si>
+    <t>Incluído Gerenciador de lançamentos, permitindo edição e exclusão de dados da planilha,</t>
+  </si>
+  <si>
+    <t>Adicionados campos na planilha com 'STATUS', 'ID_LANCAMENTO' e 'HISTORICO_ALTERACAO',</t>
+  </si>
+  <si>
+    <t>Modificados todos relatórios para identificar o 'STATUS' dos lançamentos,</t>
+  </si>
+  <si>
+    <t>Liberado Relatório por Categoria</t>
+  </si>
+  <si>
+    <t>Instalado sistema de Backup Automático contra quedas/travamentos</t>
+  </si>
+  <si>
+    <t>Melhoria no relatório de Tipos de Despesas, mostrando o total geral por tipo e gráfico de linha do tempo</t>
+  </si>
+  <si>
+    <t>Melhoria no relatório de Categoria, mostrando o total geral por categoria e gráfico de linha do tempo</t>
+  </si>
+  <si>
+    <t>Inclusão de Visualizador de Lançamentos de Fornecedor</t>
+  </si>
+  <si>
+    <t>Adicão de funcionalidade para cadastro de fornecedor PF sem CPF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melhoria no Relatório de Fornecedores com a inclusão de opção para mostrar quais clientes adquiriram itens de um dado fornecedor </t>
+  </si>
+  <si>
+    <t>Inclusão de Correção Monetária para contratos de administração, dependendo de teste para ser totalmente implementada.</t>
+  </si>
+  <si>
+    <t>Inclusão de Importação de planilha com dados de TRANSPORTE e CAFÉ</t>
+  </si>
+  <si>
+    <t>Alteração do Relatório de Despesas para incluir o PDF Temporário</t>
+  </si>
+  <si>
+    <t>Exclusão do ordenamento dos pagamentos de Diaristas para ser pela entrada e não por valor pago</t>
+  </si>
+  <si>
+    <t>Exclusão do ordenamento dos pagamentos das despesas pagas pelo Cliente para ser pela entrada e não por data de vencimento</t>
+  </si>
+  <si>
+    <t>Melhoria no Visualizador de Lançamentos de Fornecedor que agora possui todas as funcionalidades do Gerenciador de Lançamentos</t>
+  </si>
+  <si>
+    <t>Correção na aba Entrada de Dados que não estava limpando corretamente todos os campos</t>
+  </si>
+  <si>
+    <t>Inclusão de autocompletar nos campos 'Etapa da Obra' e 'Insumo' na aba Entrada de Dados</t>
+  </si>
+  <si>
+    <t>Correção de EXCLUIR/RESTAURAR individual no Gerenciador de Lançamentos</t>
+  </si>
+  <si>
+    <t>Correção do Backup Automático para verificar o Cliente antes de salvar</t>
+  </si>
+  <si>
+    <t>Inclusão da opção Dinheiro em Dados Bancários na entrada de dados</t>
+  </si>
+  <si>
+    <t>Melhorias no parcelamento, permitindo a entrada de parcelas com diferentes valores</t>
+  </si>
+  <si>
+    <t>Inclusão de Agenda com dados pré-definidos e lançamentos futuros</t>
+  </si>
+  <si>
+    <t>Correção do filtro de datas do Gerenciador de Lançamentos, que estava trazendo a data do dia se, outras funcionalidades fossem chamadas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correção da compensação de Taxa de Administração caso fossem detectados valores errados em períodos anteriores </t>
+  </si>
+  <si>
+    <t>Inclusão de edição de Taxa de Administração do tipo Fixo</t>
+  </si>
+  <si>
+    <t>Melhoria no Visualizador de Lançamentos de Pendentes, que elimina registros duplicados ao salvar na planilha</t>
+  </si>
+  <si>
+    <t>Correção na importação de dados de RH após mudança de versão do Excel na origem do arquivo</t>
+  </si>
+  <si>
+    <t>Inclusão de campo para Notas no final do relatório,</t>
+  </si>
+  <si>
+    <t>Correção para inclusão de lançamentos futuros no relatório</t>
+  </si>
+  <si>
+    <t>Inclusão de vinculação de medições de contratos à despesa lançada,</t>
+  </si>
+  <si>
+    <t>Adição de diferenciação visual entre ambientes TESTE e PRODUÇÃO</t>
+  </si>
+  <si>
+    <t>Inclusão de Etapa da Obra nas importações de dados de RH - Folha e Transporte &amp; Café,</t>
+  </si>
+  <si>
+    <t>Correção dos dados bancários na Agenda,</t>
+  </si>
+  <si>
+    <t>Inclusão da opção de remover vários regitros de uma vez só no Visualizador de Lançamentos,</t>
+  </si>
+  <si>
+    <t>Inclusão da opção de vincular parcelas do contrato de administração de obra a lançamentos efetuados,</t>
+  </si>
+  <si>
+    <t>Relatório de Despesas Aprimorado: adição de numeração de páginas,</t>
+  </si>
+  <si>
+    <t>Relatório de Despesas Aprimorado: mudança de Notas para a primeira página e arquivada na planilha do cliente,</t>
+  </si>
+  <si>
+    <t>Relatório de Despesas Aprimorado: adição de data de vencimento para 13º, Férias e Rescisão,</t>
+  </si>
+  <si>
+    <t>Mudança do botão 'Visualizar Lançamentos' para a seção de Gerenciamento de Dados</t>
+  </si>
+  <si>
+    <t>Alteração do texto Complemento de Caixa para Despesas pagas pelo Caixa no Relatório de Despesas</t>
+  </si>
+  <si>
+    <t>Inclusão de checkbox para desmarcar agrupamento de medição na Agenda, principalmente, em casos de adiantamento,</t>
+  </si>
+  <si>
+    <t>Relatório por Etapa da Obra com ferramenta interna que possibilita a correção de lançamentos antigos, com a inclusão da etapa pertinente,</t>
+  </si>
+  <si>
+    <t>Melhoria no comportamento de janelas de mensagens que, em algumas telas, ficavam ocultas,</t>
+  </si>
+  <si>
+    <t>Melhoria na seleção de lançamentos aptos para vincular medições, excluíndo os registros com STATUS = LANÇADO</t>
+  </si>
+  <si>
+    <t>Melhoria nos critérios de detectar duplicidade, admitindo pequenas variações de grafia para comparação de similaridade,</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -538,12 +616,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF292929"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -560,11 +632,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
     <font>
       <sz val="11"/>
@@ -585,12 +652,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -605,7 +678,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -628,20 +701,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -649,6 +725,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFFCC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -957,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E176"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -988,7 +1069,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1002,40 +1083,40 @@
         <v>45730</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="E9" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>1</v>
       </c>
@@ -1049,55 +1130,55 @@
         <v>45771</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E11" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E12" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E13" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E14" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E15" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E16" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E17" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E18" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E19" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>1</v>
       </c>
@@ -1114,22 +1195,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E21" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E22" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E23" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>1</v>
       </c>
@@ -1143,25 +1224,25 @@
         <v>45806</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="E25" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E26" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E27" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>1</v>
       </c>
@@ -1175,20 +1256,20 @@
         <v>45812</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="E29" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="E30" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>1</v>
       </c>
@@ -1202,27 +1283,27 @@
         <v>45824</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="E32" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
       <c r="E33" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="E34" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>1</v>
       </c>
@@ -1236,104 +1317,104 @@
         <v>45847</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E36" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="E37" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="E38" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>1</v>
       </c>
       <c r="B39" s="2">
+        <v>3</v>
+      </c>
+      <c r="C39" s="2">
         <v>4</v>
       </c>
-      <c r="C39" s="2">
+      <c r="D39" s="3">
+        <v>45860</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E40" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>1</v>
+      </c>
+      <c r="B41" s="2">
+        <v>4</v>
+      </c>
+      <c r="C41" s="2">
         <v>0</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D41" s="3">
         <v>45891</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E40" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E41" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="E42" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E43" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E44" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="E45" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E46" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E46" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="E47" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E48" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>1</v>
-      </c>
-      <c r="B48" s="2">
-        <v>4</v>
-      </c>
-      <c r="C48" s="2">
-        <v>1</v>
-      </c>
-      <c r="D48" s="3">
-        <v>45897</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="E49" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>1</v>
       </c>
@@ -1341,397 +1422,397 @@
         <v>4</v>
       </c>
       <c r="C50" s="2">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3">
+        <v>45897</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E51" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="13">
+        <v>1</v>
+      </c>
+      <c r="B52" s="13">
+        <v>4</v>
+      </c>
+      <c r="C52" s="13">
         <v>2</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D52" s="3">
         <v>45905</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E51" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E52" s="1" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>1</v>
-      </c>
-      <c r="B53" s="2">
+      <c r="E53" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E54" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>1</v>
+      </c>
+      <c r="B55" s="2">
         <v>4</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C55" s="2">
         <v>3</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D55" s="3">
         <v>45924</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E54" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E55" s="1" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>1</v>
-      </c>
-      <c r="B56" s="2">
+      <c r="E56" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E57" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>1</v>
+      </c>
+      <c r="B58" s="2">
         <v>4</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C58" s="2">
         <v>4</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D58" s="3">
         <v>45947</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E57" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E58" s="1" t="s">
-        <v>58</v>
+        <v>148</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E59" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E60" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <v>1</v>
-      </c>
-      <c r="B61" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E61" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E62" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>1</v>
+      </c>
+      <c r="B63" s="2">
         <v>4</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C63" s="2">
         <v>5</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D63" s="3">
         <v>45957</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D62" s="11"/>
-      <c r="E62" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E63" s="1" t="s">
-        <v>65</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D64" s="11"/>
       <c r="E64" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
-        <v>1</v>
-      </c>
-      <c r="B65" s="2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E65" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E66" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>1</v>
+      </c>
+      <c r="B67" s="2">
         <v>5</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C67" s="2">
         <v>0</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D67" s="3">
         <v>45976</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E66" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E67" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E68" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E68" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E69" s="1" t="s">
-        <v>71</v>
+        <v>159</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E70" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E71" s="1" t="s">
-        <v>73</v>
+        <v>161</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E72" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>1</v>
-      </c>
-      <c r="B73" s="2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E73" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E74" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>1</v>
+      </c>
+      <c r="B75" s="2">
         <v>5</v>
       </c>
-      <c r="C73" s="2">
-        <v>1</v>
-      </c>
-      <c r="D73" s="3">
+      <c r="C75" s="2">
+        <v>1</v>
+      </c>
+      <c r="D75" s="3">
         <v>45992</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E74" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E75" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E75" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E76" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E77" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
-        <v>1</v>
-      </c>
-      <c r="B78" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E78" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E79" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>1</v>
+      </c>
+      <c r="B80" s="2">
         <v>5</v>
       </c>
-      <c r="C78" s="2">
+      <c r="C80" s="2">
         <v>2</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D80" s="3">
         <v>46009</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E79" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E80" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E81" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E82" s="1" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E83" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E84" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E85" s="1" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E86" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E87" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E88" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E89" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E90" s="1" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
-        <v>1</v>
-      </c>
-      <c r="B91" s="2">
-        <v>5</v>
-      </c>
-      <c r="C91" s="2">
-        <v>3</v>
-      </c>
-      <c r="D91" s="3">
-        <v>46034</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E92" s="1" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>1</v>
+      </c>
+      <c r="B93" s="2">
+        <v>5</v>
+      </c>
+      <c r="C93" s="2">
+        <v>3</v>
+      </c>
+      <c r="D93" s="3">
+        <v>46034</v>
+      </c>
       <c r="E93" s="1" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E94" s="1" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E95" s="1" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E96" s="1" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E97" s="1" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
-        <v>1</v>
-      </c>
-      <c r="B98" s="2">
-        <v>6</v>
-      </c>
-      <c r="C98" s="2">
-        <v>0</v>
-      </c>
-      <c r="D98" s="3">
-        <v>46042</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E99" s="1" t="s">
-        <v>101</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>1</v>
+      </c>
+      <c r="B100" s="2">
+        <v>6</v>
+      </c>
+      <c r="C100" s="2">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3">
+        <v>46042</v>
+      </c>
       <c r="E100" s="1" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E101" s="1" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E102" s="1" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E103" s="1" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
-        <v>1</v>
-      </c>
-      <c r="B104" s="2">
-        <v>6</v>
-      </c>
-      <c r="C104" s="2">
-        <v>1</v>
-      </c>
-      <c r="D104" s="3">
-        <v>46058</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E105" s="1" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -1739,21 +1820,21 @@
         <v>1</v>
       </c>
       <c r="B106" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C106" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106" s="3">
-        <v>46075</v>
+        <v>46058</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>107</v>
+        <v>35</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E107" s="1" t="s">
-        <v>108</v>
+        <v>36</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -1764,151 +1845,504 @@
         <v>7</v>
       </c>
       <c r="C108" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108" s="3">
-        <v>46077</v>
+        <v>46075</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>110</v>
+        <v>37</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E109" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>1</v>
+      </c>
+      <c r="B110" s="2">
+        <v>7</v>
+      </c>
+      <c r="C110" s="2">
+        <v>1</v>
+      </c>
+      <c r="D110" s="3">
+        <v>46077</v>
+      </c>
       <c r="E110" s="1" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
-        <v>1</v>
-      </c>
-      <c r="B111" s="2">
+      <c r="E111" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E112" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>1</v>
+      </c>
+      <c r="B113" s="2">
         <v>7</v>
       </c>
-      <c r="C111" s="2">
+      <c r="C113" s="2">
         <v>2</v>
       </c>
-      <c r="D111" s="3">
+      <c r="D113" s="3">
         <v>46084</v>
       </c>
-      <c r="E111" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E112" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E113" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E114" s="1" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
-        <v>1</v>
-      </c>
-      <c r="B115" s="2">
+      <c r="E115" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E116" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <v>1</v>
+      </c>
+      <c r="B117" s="2">
         <v>7</v>
       </c>
-      <c r="C115" s="2">
+      <c r="C117" s="2">
         <v>3</v>
       </c>
-      <c r="D115" s="3">
+      <c r="D117" s="3">
         <v>46120</v>
       </c>
-      <c r="E115" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E116" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E117" s="1" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E118" s="1" t="s">
-        <v>126</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E119" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
-        <v>1</v>
-      </c>
-      <c r="B120" s="2">
+      <c r="E120" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
+        <v>1</v>
+      </c>
+      <c r="B122" s="2">
         <v>7</v>
       </c>
-      <c r="C120" s="2">
+      <c r="C122" s="2">
         <v>4</v>
       </c>
-      <c r="D120" s="3">
+      <c r="D122" s="3">
         <v>46164</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E121" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E122" s="12" t="s">
-        <v>121</v>
+      <c r="E122" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E123" s="12" t="s">
-        <v>122</v>
+      <c r="E123" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
-        <v>1</v>
-      </c>
-      <c r="B124" s="2">
+      <c r="E124" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E125" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
+        <v>1</v>
+      </c>
+      <c r="B126" s="2">
         <v>7</v>
       </c>
-      <c r="C124" s="2">
+      <c r="C126" s="2">
         <v>5</v>
       </c>
-      <c r="D124" s="3">
+      <c r="D126" s="3">
         <v>46183</v>
       </c>
-      <c r="E124" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E125" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E126" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E127" s="1" t="s">
-        <v>118</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E128" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E129" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A130" s="2">
+        <v>1</v>
+      </c>
+      <c r="B130" s="2">
+        <v>7</v>
+      </c>
+      <c r="C130" s="2">
+        <v>6</v>
+      </c>
+      <c r="D130" s="3">
+        <v>46197</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E131" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E132" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E133" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E134" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E135" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E136" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A137" s="2">
+        <v>1</v>
+      </c>
+      <c r="B137" s="2">
+        <v>7</v>
+      </c>
+      <c r="C137" s="2">
+        <v>7</v>
+      </c>
+      <c r="D137" s="3">
+        <v>46202</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E138" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E139" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E140" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E141" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E142" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E143" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E144" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A145" s="2">
+        <v>1</v>
+      </c>
+      <c r="B145" s="2">
+        <v>8</v>
+      </c>
+      <c r="C145" s="2">
+        <v>0</v>
+      </c>
+      <c r="D145" s="3">
+        <v>46211</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E146" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E147" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E148" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A149" s="2">
+        <v>1</v>
+      </c>
+      <c r="B149" s="2">
+        <v>8</v>
+      </c>
+      <c r="C149" s="2">
+        <v>1</v>
+      </c>
+      <c r="D149" s="3">
+        <v>46225</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E150" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E151" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E152" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E153" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E154" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E155" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E156" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E157" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E158" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E159" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="2">
+        <v>1</v>
+      </c>
+      <c r="B160" s="2">
+        <v>8</v>
+      </c>
+      <c r="C160" s="2">
+        <v>2</v>
+      </c>
+      <c r="D160" s="3">
+        <v>46236</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E161" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E162" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E163" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E164" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="2">
+        <v>1</v>
+      </c>
+      <c r="B165" s="2">
+        <v>8</v>
+      </c>
+      <c r="C165" s="2">
+        <v>3</v>
+      </c>
+      <c r="D165" s="3">
+        <v>46254</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E166" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E167" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E168" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A169" s="2">
+        <v>1</v>
+      </c>
+      <c r="B169" s="2">
+        <v>8</v>
+      </c>
+      <c r="C169" s="2">
+        <v>4</v>
+      </c>
+      <c r="D169" s="3">
+        <v>46280</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E170" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E171" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A172" s="2">
+        <v>1</v>
+      </c>
+      <c r="B172" s="2">
+        <v>8</v>
+      </c>
+      <c r="C172" s="2">
+        <v>5</v>
+      </c>
+      <c r="D172" s="3">
+        <v>46290</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E173" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E174" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E175" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E176" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
